--- a/Resources/data/loginData.xlsx
+++ b/Resources/data/loginData.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="6">
   <si>
     <t>Email</t>
   </si>

--- a/Resources/data/loginData.xlsx
+++ b/Resources/data/loginData.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="6">
   <si>
     <t>Email</t>
   </si>

--- a/Resources/data/loginData.xlsx
+++ b/Resources/data/loginData.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="6">
   <si>
     <t>Email</t>
   </si>

--- a/Resources/data/loginData.xlsx
+++ b/Resources/data/loginData.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="6">
   <si>
     <t>Email</t>
   </si>
